--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/83.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/83.xlsx
@@ -426,13 +426,13 @@
         <v>2.381954749345109</v>
       </c>
       <c r="E2">
-        <v>-10.74262472818952</v>
+        <v>1.415499271661983</v>
       </c>
       <c r="F2">
-        <v>-3.851200316135815</v>
+        <v>-1.587573730019386</v>
       </c>
       <c r="G2">
-        <v>-11.9451809814855</v>
+        <v>-6.909503379091934</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>2.83208890626325</v>
       </c>
       <c r="E3">
-        <v>-10.82968916946099</v>
+        <v>0.8944304099693934</v>
       </c>
       <c r="F3">
-        <v>-3.923183786704287</v>
+        <v>-1.607022968269715</v>
       </c>
       <c r="G3">
-        <v>-12.47164641825529</v>
+        <v>-6.397819845447446</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.192378599999311</v>
       </c>
       <c r="E4">
-        <v>-12.18198207763152</v>
+        <v>-0.6869987545152412</v>
       </c>
       <c r="F4">
-        <v>-3.545294174690791</v>
+        <v>-1.862725074900672</v>
       </c>
       <c r="G4">
-        <v>-12.15631774517109</v>
+        <v>-6.112553724290883</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.412197243210524</v>
       </c>
       <c r="E5">
-        <v>-12.42007112705879</v>
+        <v>-1.691654298538933</v>
       </c>
       <c r="F5">
-        <v>-3.751874094335738</v>
+        <v>-1.674138951979337</v>
       </c>
       <c r="G5">
-        <v>-12.30401209000482</v>
+        <v>-5.628297921661794</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.530588024640759</v>
       </c>
       <c r="E6">
-        <v>-12.78801869713002</v>
+        <v>-2.569770693366292</v>
       </c>
       <c r="F6">
-        <v>-3.467533669855196</v>
+        <v>-1.758105585396706</v>
       </c>
       <c r="G6">
-        <v>-11.95681619313529</v>
+        <v>-6.005904179944251</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.563554165273179</v>
       </c>
       <c r="E7">
-        <v>-13.01916106742953</v>
+        <v>-3.891854151431645</v>
       </c>
       <c r="F7">
-        <v>-3.442373666729967</v>
+        <v>-1.036043399765863</v>
       </c>
       <c r="G7">
-        <v>-11.83442334774644</v>
+        <v>-5.494050022778673</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.537967959766307</v>
       </c>
       <c r="E8">
-        <v>-13.91535965896952</v>
+        <v>-2.964187194012357</v>
       </c>
       <c r="F8">
-        <v>-3.031278947375253</v>
+        <v>-1.313266491521552</v>
       </c>
       <c r="G8">
-        <v>-11.95658322640457</v>
+        <v>-5.450124309762386</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.476108136544151</v>
       </c>
       <c r="E9">
-        <v>-14.05677937375506</v>
+        <v>-3.745081780369041</v>
       </c>
       <c r="F9">
-        <v>-3.039918819386452</v>
+        <v>-1.230392474708475</v>
       </c>
       <c r="G9">
-        <v>-11.90470711354975</v>
+        <v>-6.077844962635076</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.40575914145019</v>
       </c>
       <c r="E10">
-        <v>-14.80583425936381</v>
+        <v>-4.823913728638374</v>
       </c>
       <c r="F10">
-        <v>-3.276002700816909</v>
+        <v>-1.206246393284272</v>
       </c>
       <c r="G10">
-        <v>-12.05700829345294</v>
+        <v>-4.893727569927345</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.349886104180805</v>
       </c>
       <c r="E11">
-        <v>-15.01917066986516</v>
+        <v>-6.602535293787014</v>
       </c>
       <c r="F11">
-        <v>-2.986474211292634</v>
+        <v>-1.137346106189021</v>
       </c>
       <c r="G11">
-        <v>-11.62329314650398</v>
+        <v>-3.599118322426873</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.330759278325723</v>
       </c>
       <c r="E12">
-        <v>-16.64632383640524</v>
+        <v>-6.661532253158943</v>
       </c>
       <c r="F12">
-        <v>-2.500294613813367</v>
+        <v>-0.9672408600241421</v>
       </c>
       <c r="G12">
-        <v>-10.8895988809259</v>
+        <v>-4.099691639871081</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.361673383557612</v>
       </c>
       <c r="E13">
-        <v>-16.79980287747321</v>
+        <v>-7.358944421184225</v>
       </c>
       <c r="F13">
-        <v>-2.433252354802595</v>
+        <v>-0.4890608065537106</v>
       </c>
       <c r="G13">
-        <v>-10.76258607558135</v>
+        <v>-3.396181331418337</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.447160499367922</v>
       </c>
       <c r="E14">
-        <v>-17.50724108695147</v>
+        <v>-8.520226295711211</v>
       </c>
       <c r="F14">
-        <v>-2.415936162614474</v>
+        <v>-0.2544845537963495</v>
       </c>
       <c r="G14">
-        <v>-10.6680015829088</v>
+        <v>-3.248165426871786</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.578296061160712</v>
       </c>
       <c r="E15">
-        <v>-17.93980092416415</v>
+        <v>-9.559089932388844</v>
       </c>
       <c r="F15">
-        <v>-1.548913823330732</v>
+        <v>-0.1643217322060401</v>
       </c>
       <c r="G15">
-        <v>-10.66378521320491</v>
+        <v>-2.780184483177543</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.734978320534725</v>
       </c>
       <c r="E16">
-        <v>-18.43915575298995</v>
+        <v>-9.230155165893693</v>
       </c>
       <c r="F16">
-        <v>-2.058700235054979</v>
+        <v>0.2834183043137179</v>
       </c>
       <c r="G16">
-        <v>-10.13668978189571</v>
+        <v>-2.005760414382079</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.886901019555161</v>
       </c>
       <c r="E17">
-        <v>-19.14919783502263</v>
+        <v>-11.30050102661646</v>
       </c>
       <c r="F17">
-        <v>-1.541941454901369</v>
+        <v>0.51978797249814</v>
       </c>
       <c r="G17">
-        <v>-9.387514713000177</v>
+        <v>-0.7141862968240934</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.000770240129676</v>
       </c>
       <c r="E18">
-        <v>-19.90410350904929</v>
+        <v>-11.67681268817986</v>
       </c>
       <c r="F18">
-        <v>-1.105659396297134</v>
+        <v>0.5745165500662978</v>
       </c>
       <c r="G18">
-        <v>-9.248850289898044</v>
+        <v>-1.709269234270655</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.045840564398662</v>
       </c>
       <c r="E19">
-        <v>-21.09559483368145</v>
+        <v>-12.7685779582151</v>
       </c>
       <c r="F19">
-        <v>-1.05797442675498</v>
+        <v>1.145791845732949</v>
       </c>
       <c r="G19">
-        <v>-8.60703350920598</v>
+        <v>-0.8913919483634647</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.003227115910562</v>
       </c>
       <c r="E20">
-        <v>-21.61543647891796</v>
+        <v>-13.46460894166804</v>
       </c>
       <c r="F20">
-        <v>-0.4234408543735451</v>
+        <v>1.182665792301166</v>
       </c>
       <c r="G20">
-        <v>-8.777985152453049</v>
+        <v>-0.7729201627381538</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.870024261400216</v>
       </c>
       <c r="E21">
-        <v>-22.15712348276747</v>
+        <v>-14.10858964487682</v>
       </c>
       <c r="F21">
-        <v>-0.09926258475756972</v>
+        <v>1.627207502278715</v>
       </c>
       <c r="G21">
-        <v>-7.579043200739747</v>
+        <v>-0.6740241449364901</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.660016487029152</v>
       </c>
       <c r="E22">
-        <v>-22.2024806784283</v>
+        <v>-14.62742596888362</v>
       </c>
       <c r="F22">
-        <v>-0.1729806566675033</v>
+        <v>1.671772011814523</v>
       </c>
       <c r="G22">
-        <v>-8.407394145864684</v>
+        <v>-0.7330434771262222</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.398353902663706</v>
       </c>
       <c r="E23">
-        <v>-22.97710332828436</v>
+        <v>-16.20732450915366</v>
       </c>
       <c r="F23">
-        <v>-0.02601999573684302</v>
+        <v>1.820278406318807</v>
       </c>
       <c r="G23">
-        <v>-7.862967302278498</v>
+        <v>-0.3167253668854361</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.118713492933788</v>
       </c>
       <c r="E24">
-        <v>-23.543660711384</v>
+        <v>-16.63863901601423</v>
       </c>
       <c r="F24">
-        <v>-0.09013231924391356</v>
+        <v>2.057274320259745</v>
       </c>
       <c r="G24">
-        <v>-8.403591210077288</v>
+        <v>-0.3346703675940392</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.8572552002106</v>
       </c>
       <c r="E25">
-        <v>-23.20261227691833</v>
+        <v>-15.05533053481641</v>
       </c>
       <c r="F25">
-        <v>0.06436482831741663</v>
+        <v>2.26337710028068</v>
       </c>
       <c r="G25">
-        <v>-7.525270541823567</v>
+        <v>0.1059878441747078</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.646388586769131</v>
       </c>
       <c r="E26">
-        <v>-23.40050206257952</v>
+        <v>-15.8992252515678</v>
       </c>
       <c r="F26">
-        <v>-0.1167088306279301</v>
+        <v>2.89081073565272</v>
       </c>
       <c r="G26">
-        <v>-8.380622659161174</v>
+        <v>0.2731595201852972</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.510231587723196</v>
       </c>
       <c r="E27">
-        <v>-23.24018049728596</v>
+        <v>-16.86684693515677</v>
       </c>
       <c r="F27">
-        <v>-0.1290117432943084</v>
+        <v>2.357395143763618</v>
       </c>
       <c r="G27">
-        <v>-8.376836129481577</v>
+        <v>-0.7018193727665463</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.460505543506671</v>
       </c>
       <c r="E28">
-        <v>-23.41642870566449</v>
+        <v>-16.98941914112238</v>
       </c>
       <c r="F28">
-        <v>-0.1362235099030809</v>
+        <v>2.524402295842026</v>
       </c>
       <c r="G28">
-        <v>-8.017729398351268</v>
+        <v>-1.558592259039394</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.498157684270088</v>
       </c>
       <c r="E29">
-        <v>-23.1787426904239</v>
+        <v>-14.90501689707981</v>
       </c>
       <c r="F29">
-        <v>-0.2931022137474597</v>
+        <v>2.498398186333344</v>
       </c>
       <c r="G29">
-        <v>-8.331945737326812</v>
+        <v>-1.521708047489676</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.611229708333328</v>
       </c>
       <c r="E30">
-        <v>-23.92159356664214</v>
+        <v>-14.57893054073548</v>
       </c>
       <c r="F30">
-        <v>-0.2273944546225972</v>
+        <v>2.363366016002996</v>
       </c>
       <c r="G30">
-        <v>-7.989714328676729</v>
+        <v>-1.71839431142747</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.778501291938852</v>
       </c>
       <c r="E31">
-        <v>-22.9855715746787</v>
+        <v>-16.30002237209068</v>
       </c>
       <c r="F31">
-        <v>-0.434555059816906</v>
+        <v>2.422592628568355</v>
       </c>
       <c r="G31">
-        <v>-8.63025471418217</v>
+        <v>-1.200610986903975</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.971548078397413</v>
       </c>
       <c r="E32">
-        <v>-23.34262816476149</v>
+        <v>-13.79981564466381</v>
       </c>
       <c r="F32">
-        <v>-0.473644060820209</v>
+        <v>1.947229024267443</v>
       </c>
       <c r="G32">
-        <v>-8.542737972748659</v>
+        <v>-0.2783974178495623</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.161637781348465</v>
       </c>
       <c r="E33">
-        <v>-22.30122858263956</v>
+        <v>-14.41889426930441</v>
       </c>
       <c r="F33">
-        <v>-0.3320926390298296</v>
+        <v>2.118179205183176</v>
       </c>
       <c r="G33">
-        <v>-8.501191145362972</v>
+        <v>-1.084048872226261</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.319844181792571</v>
       </c>
       <c r="E34">
-        <v>-22.8650734098086</v>
+        <v>-13.73795668971903</v>
       </c>
       <c r="F34">
-        <v>-0.3414374517008108</v>
+        <v>2.276700561587307</v>
       </c>
       <c r="G34">
-        <v>-8.401284511320998</v>
+        <v>-0.9534726602681587</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.419214119048016</v>
       </c>
       <c r="E35">
-        <v>-21.8479555053158</v>
+        <v>-14.48761386237081</v>
       </c>
       <c r="F35">
-        <v>-0.4832415255490441</v>
+        <v>2.172019772895533</v>
       </c>
       <c r="G35">
-        <v>-8.447815514255485</v>
+        <v>-0.6040225641872965</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.437723714150395</v>
       </c>
       <c r="E36">
-        <v>-21.77490216262406</v>
+        <v>-13.06119436316873</v>
       </c>
       <c r="F36">
-        <v>-0.2563218726957588</v>
+        <v>2.509957225072008</v>
       </c>
       <c r="G36">
-        <v>-8.358270977898238</v>
+        <v>-0.2019580804007383</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.360625888359823</v>
       </c>
       <c r="E37">
-        <v>-21.29126566707888</v>
+        <v>-13.81490452005737</v>
       </c>
       <c r="F37">
-        <v>-0.5930043482569927</v>
+        <v>2.246224924838313</v>
       </c>
       <c r="G37">
-        <v>-8.381242810035911</v>
+        <v>-0.4676484337336552</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.181683509461314</v>
       </c>
       <c r="E38">
-        <v>-21.58188501499513</v>
+        <v>-13.16543530635129</v>
       </c>
       <c r="F38">
-        <v>0.006649157894763879</v>
+        <v>1.992211030974261</v>
       </c>
       <c r="G38">
-        <v>-8.344571877887557</v>
+        <v>-0.9819536634041388</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.903441856045549</v>
       </c>
       <c r="E39">
-        <v>-21.21656395984835</v>
+        <v>-12.29451465672212</v>
       </c>
       <c r="F39">
-        <v>-0.3620546879890877</v>
+        <v>2.001937721017933</v>
       </c>
       <c r="G39">
-        <v>-8.181541103484985</v>
+        <v>-0.2043796219116085</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.539776054513361</v>
       </c>
       <c r="E40">
-        <v>-20.93362943232311</v>
+        <v>-11.38377513514351</v>
       </c>
       <c r="F40">
-        <v>-0.2006787775149104</v>
+        <v>2.318753461157826</v>
       </c>
       <c r="G40">
-        <v>-8.462243045452363</v>
+        <v>-0.386618667323168</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.112657106311203</v>
       </c>
       <c r="E41">
-        <v>-19.99085548561423</v>
+        <v>-10.98713968223368</v>
       </c>
       <c r="F41">
-        <v>-0.1844477466244569</v>
+        <v>2.248825998483103</v>
       </c>
       <c r="G41">
-        <v>-7.925960193776718</v>
+        <v>-0.2252645971374741</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.648241938014564</v>
       </c>
       <c r="E42">
-        <v>-20.05325332896592</v>
+        <v>-11.67745120301494</v>
       </c>
       <c r="F42">
-        <v>-0.4199302333204807</v>
+        <v>2.11954435466299</v>
       </c>
       <c r="G42">
-        <v>-7.936040106407332</v>
+        <v>0.01140991394527327</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.172506456724738</v>
       </c>
       <c r="E43">
-        <v>-20.14469680460281</v>
+        <v>-10.43373298765232</v>
       </c>
       <c r="F43">
-        <v>-0.2480274298915273</v>
+        <v>2.231368983836507</v>
       </c>
       <c r="G43">
-        <v>-7.731511722942464</v>
+        <v>0.2127325439465632</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.7121180855537104</v>
       </c>
       <c r="E44">
-        <v>-19.67328266040433</v>
+        <v>-9.447517389787862</v>
       </c>
       <c r="F44">
-        <v>-0.6430128883639988</v>
+        <v>1.71532425638411</v>
       </c>
       <c r="G44">
-        <v>-7.742270848435884</v>
+        <v>0.6673982905525797</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.2879366914264484</v>
       </c>
       <c r="E45">
-        <v>-19.35086889648022</v>
+        <v>-10.39683498143782</v>
       </c>
       <c r="F45">
-        <v>-0.5298148260366408</v>
+        <v>2.177765329201351</v>
       </c>
       <c r="G45">
-        <v>-7.120151240765166</v>
+        <v>0.1485781000163002</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.08781134954329188</v>
       </c>
       <c r="E46">
-        <v>-19.02839626239401</v>
+        <v>-9.770447399748843</v>
       </c>
       <c r="F46">
-        <v>-0.5360325517620539</v>
+        <v>2.140555065467597</v>
       </c>
       <c r="G46">
-        <v>-7.654235673995982</v>
+        <v>0.4335784422265493</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.4103041961854078</v>
       </c>
       <c r="E47">
-        <v>-18.09021418832891</v>
+        <v>-9.033008049969764</v>
       </c>
       <c r="F47">
-        <v>-0.6436747539188356</v>
+        <v>1.971543264274414</v>
       </c>
       <c r="G47">
-        <v>-7.1563463957874</v>
+        <v>0.5189919206404546</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.6791422383943092</v>
       </c>
       <c r="E48">
-        <v>-18.30708733703026</v>
+        <v>-7.692548044381284</v>
       </c>
       <c r="F48">
-        <v>-0.8744040684575959</v>
+        <v>1.749323768064613</v>
       </c>
       <c r="G48">
-        <v>-6.883909850928265</v>
+        <v>0.212184579946136</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.8987556727853374</v>
       </c>
       <c r="E49">
-        <v>-17.58366361430492</v>
+        <v>-8.923215197653796</v>
       </c>
       <c r="F49">
-        <v>-0.81461913626275</v>
+        <v>1.561246262728596</v>
       </c>
       <c r="G49">
-        <v>-7.330772852665922</v>
+        <v>0.8992034688411111</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.078565803336817</v>
       </c>
       <c r="E50">
-        <v>-17.16838443390552</v>
+        <v>-7.65842146425948</v>
       </c>
       <c r="F50">
-        <v>-0.5898515819219378</v>
+        <v>1.646644315018003</v>
       </c>
       <c r="G50">
-        <v>-7.075618501760382</v>
+        <v>1.482627630661298</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.227611635993372</v>
       </c>
       <c r="E51">
-        <v>-17.08128829331599</v>
+        <v>-6.04333668094984</v>
       </c>
       <c r="F51">
-        <v>-0.7822250006088725</v>
+        <v>1.505051474857483</v>
       </c>
       <c r="G51">
-        <v>-7.00076399432477</v>
+        <v>0.255244050470729</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.352374459885148</v>
       </c>
       <c r="E52">
-        <v>-16.07977551025362</v>
+        <v>-7.58974715593316</v>
       </c>
       <c r="F52">
-        <v>-0.8514326120105628</v>
+        <v>1.564761853986077</v>
       </c>
       <c r="G52">
-        <v>-7.282781706137484</v>
+        <v>1.296743148097195</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.456750431093001</v>
       </c>
       <c r="E53">
-        <v>-16.13825622358868</v>
+        <v>-6.077811953570234</v>
       </c>
       <c r="F53">
-        <v>-1.014193552782221</v>
+        <v>1.722479694009492</v>
       </c>
       <c r="G53">
-        <v>-6.725305444409386</v>
+        <v>0.648865951184836</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.541072633574325</v>
       </c>
       <c r="E54">
-        <v>-15.1218628749371</v>
+        <v>-6.136587017715788</v>
       </c>
       <c r="F54">
-        <v>-1.14737680706952</v>
+        <v>1.228020564339245</v>
       </c>
       <c r="G54">
-        <v>-7.166426308418014</v>
+        <v>0.7357264483064565</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.600044853289435</v>
       </c>
       <c r="E55">
-        <v>-15.28872808517174</v>
+        <v>-5.392440997931349</v>
       </c>
       <c r="F55">
-        <v>-1.095506925408423</v>
+        <v>1.457594306351099</v>
       </c>
       <c r="G55">
-        <v>-7.111524909285386</v>
+        <v>0.3590520569468815</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.627945116316759</v>
       </c>
       <c r="E56">
-        <v>-15.19267462299505</v>
+        <v>-5.275918833239983</v>
       </c>
       <c r="F56">
-        <v>-1.216851152774912</v>
+        <v>1.292069931923702</v>
       </c>
       <c r="G56">
-        <v>-7.106160112035694</v>
+        <v>0.5660151068088569</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.622035464570842</v>
       </c>
       <c r="E57">
-        <v>-14.49909354398025</v>
+        <v>-5.047470904975036</v>
       </c>
       <c r="F57">
-        <v>-1.025701232741911</v>
+        <v>1.474665301787992</v>
       </c>
       <c r="G57">
-        <v>-7.696330465382099</v>
+        <v>-0.01235925503134425</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.582027965462353</v>
       </c>
       <c r="E58">
-        <v>-14.0233864064225</v>
+        <v>-4.279514168858266</v>
       </c>
       <c r="F58">
-        <v>-1.291010744510537</v>
+        <v>1.067451483715394</v>
       </c>
       <c r="G58">
-        <v>-7.611487919519536</v>
+        <v>0.1913028859418298</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.508937295750258</v>
       </c>
       <c r="E59">
-        <v>-15.1806062397646</v>
+        <v>-4.235003797836875</v>
       </c>
       <c r="F59">
-        <v>-0.9491120394138749</v>
+        <v>1.713322920738946</v>
       </c>
       <c r="G59">
-        <v>-8.127479697071575</v>
+        <v>-0.175321123781166</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.403958838039846</v>
       </c>
       <c r="E60">
-        <v>-13.54486255803197</v>
+        <v>-3.824284790763196</v>
       </c>
       <c r="F60">
-        <v>-1.060495148761699</v>
+        <v>1.40256917325274</v>
       </c>
       <c r="G60">
-        <v>-8.238398110667044</v>
+        <v>-0.4485714115870437</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.267368931075215</v>
       </c>
       <c r="E61">
-        <v>-13.67545016299116</v>
+        <v>-3.019103998303375</v>
       </c>
       <c r="F61">
-        <v>-0.8999500907925299</v>
+        <v>1.399366704873517</v>
       </c>
       <c r="G61">
-        <v>-8.055368290859658</v>
+        <v>-0.8104343688272853</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.099814477176981</v>
       </c>
       <c r="E62">
-        <v>-13.42173787823742</v>
+        <v>-3.142708696342738</v>
       </c>
       <c r="F62">
-        <v>-1.251430521637374</v>
+        <v>1.631775120137752</v>
       </c>
       <c r="G62">
-        <v>-8.131249820643376</v>
+        <v>-1.028904662698233</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.9033973883025909</v>
       </c>
       <c r="E63">
-        <v>-12.9346597424464</v>
+        <v>-2.720066217206864</v>
       </c>
       <c r="F63">
-        <v>-1.301056356004287</v>
+        <v>1.29481514149658</v>
       </c>
       <c r="G63">
-        <v>-8.357867387646426</v>
+        <v>-1.430785398077463</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.680544991215127</v>
       </c>
       <c r="E64">
-        <v>-13.13996264005815</v>
+        <v>-2.48377950043464</v>
       </c>
       <c r="F64">
-        <v>-1.335455140772939</v>
+        <v>1.527593008622463</v>
       </c>
       <c r="G64">
-        <v>-8.733203040609748</v>
+        <v>-1.425729035654358</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.4341211184932657</v>
       </c>
       <c r="E65">
-        <v>-12.93724550110479</v>
+        <v>-3.558988669497836</v>
       </c>
       <c r="F65">
-        <v>-1.157372716519101</v>
+        <v>1.677888676716794</v>
       </c>
       <c r="G65">
-        <v>-8.586312595058086</v>
+        <v>-1.865005853146579</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.1716939703003037</v>
       </c>
       <c r="E66">
-        <v>-13.34434172897233</v>
+        <v>-3.198404398163076</v>
       </c>
       <c r="F66">
-        <v>-1.311123505050509</v>
+        <v>1.223555664038155</v>
       </c>
       <c r="G66">
-        <v>-8.993748438537455</v>
+        <v>-1.402563611444679</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.09536057470313107</v>
       </c>
       <c r="E67">
-        <v>-12.42027943686315</v>
+        <v>-3.331129442853886</v>
       </c>
       <c r="F67">
-        <v>-1.229095251355691</v>
+        <v>1.45290740358606</v>
       </c>
       <c r="G67">
-        <v>-9.031252800961909</v>
+        <v>-1.479970909253539</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.354539039139139</v>
       </c>
       <c r="E68">
-        <v>-12.87829835494694</v>
+        <v>-3.018411141780202</v>
       </c>
       <c r="F68">
-        <v>-1.382519663130396</v>
+        <v>1.512127389212196</v>
       </c>
       <c r="G68">
-        <v>-8.814098276936297</v>
+        <v>-2.107383127299642</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.5953083939479779</v>
       </c>
       <c r="E69">
-        <v>-12.57476832763482</v>
+        <v>-2.299475136796464</v>
       </c>
       <c r="F69">
-        <v>-1.438879296114666</v>
+        <v>1.30773104604103</v>
       </c>
       <c r="G69">
-        <v>-9.068396229014823</v>
+        <v>-2.601174159780477</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.807261634861393</v>
       </c>
       <c r="E70">
-        <v>-13.29507193176887</v>
+        <v>-1.482130863152041</v>
       </c>
       <c r="F70">
-        <v>-1.387994343295498</v>
+        <v>1.264299743112252</v>
       </c>
       <c r="G70">
-        <v>-9.149737711473456</v>
+        <v>-2.248931744152527</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.9824196378841413</v>
       </c>
       <c r="E71">
-        <v>-13.12882259399928</v>
+        <v>-2.186784061115587</v>
       </c>
       <c r="F71">
-        <v>-1.421824039658427</v>
+        <v>0.9703270624719575</v>
       </c>
       <c r="G71">
-        <v>-8.640705404849001</v>
+        <v>-2.332081179690416</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.115352224498272</v>
       </c>
       <c r="E72">
-        <v>-12.94731229882384</v>
+        <v>-2.213307333378512</v>
       </c>
       <c r="F72">
-        <v>-1.544919435714433</v>
+        <v>0.9915829700277928</v>
       </c>
       <c r="G72">
-        <v>-8.454266395841353</v>
+        <v>-2.328783552023173</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.201963367065254</v>
       </c>
       <c r="E73">
-        <v>-12.27807629607428</v>
+        <v>-1.823912910406954</v>
       </c>
       <c r="F73">
-        <v>-1.498084371127552</v>
+        <v>1.406986028244467</v>
       </c>
       <c r="G73">
-        <v>-8.764788079340962</v>
+        <v>-1.984334037598905</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.238647257843595</v>
       </c>
       <c r="E74">
-        <v>-12.67200825000153</v>
+        <v>-2.015177538594919</v>
       </c>
       <c r="F74">
-        <v>-1.637174713364214</v>
+        <v>0.6816675303532194</v>
       </c>
       <c r="G74">
-        <v>-8.32965216345676</v>
+        <v>-2.798769322090237</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.223933165514188</v>
       </c>
       <c r="E75">
-        <v>-12.87731114761327</v>
+        <v>-2.484965960624649</v>
       </c>
       <c r="F75">
-        <v>-1.551055981434372</v>
+        <v>0.9818595934537323</v>
       </c>
       <c r="G75">
-        <v>-8.329304353971459</v>
+        <v>-1.495038278654509</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.158769538956391</v>
       </c>
       <c r="E76">
-        <v>-12.57543401331395</v>
+        <v>-4.077431016265977</v>
       </c>
       <c r="F76">
-        <v>-1.560792611886877</v>
+        <v>0.4528492594127176</v>
       </c>
       <c r="G76">
-        <v>-8.477540100362493</v>
+        <v>-0.7037224812710242</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.047614331750613</v>
       </c>
       <c r="E77">
-        <v>-13.07737007232413</v>
+        <v>-3.457741047634342</v>
       </c>
       <c r="F77">
-        <v>-1.903414481726184</v>
+        <v>1.122097224543272</v>
       </c>
       <c r="G77">
-        <v>-8.421076839767569</v>
+        <v>-1.713472479088303</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.8983916752482841</v>
       </c>
       <c r="E78">
-        <v>-14.11599822835336</v>
+        <v>-2.488190234118111</v>
       </c>
       <c r="F78">
-        <v>-1.781158221849213</v>
+        <v>0.5247308407906447</v>
       </c>
       <c r="G78">
-        <v>-8.122538177403051</v>
+        <v>-1.004912370655574</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.7220647467785772</v>
       </c>
       <c r="E79">
-        <v>-13.5665448915807</v>
+        <v>-4.734825059485474</v>
       </c>
       <c r="F79">
-        <v>-1.921793469292096</v>
+        <v>0.6450669450279261</v>
       </c>
       <c r="G79">
-        <v>-7.585851735475595</v>
+        <v>-0.6500876336603408</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5308822684726503</v>
       </c>
       <c r="E80">
-        <v>-14.42522054749313</v>
+        <v>-5.138955136877993</v>
       </c>
       <c r="F80">
-        <v>-1.923824626163761</v>
+        <v>0.3326142159985777</v>
       </c>
       <c r="G80">
-        <v>-8.412486601724943</v>
+        <v>-0.9932574716764259</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3375499392176151</v>
       </c>
       <c r="E81">
-        <v>-14.62696406453484</v>
+        <v>-4.469764418868513</v>
       </c>
       <c r="F81">
-        <v>-1.916751196911256</v>
+        <v>0.3327152768217193</v>
       </c>
       <c r="G81">
-        <v>-7.7093241027575</v>
+        <v>-0.6996537665373127</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.1541523340308967</v>
       </c>
       <c r="E82">
-        <v>-15.38587290958429</v>
+        <v>-5.757884321876339</v>
       </c>
       <c r="F82">
-        <v>-1.774773165908434</v>
+        <v>0.4442516341390615</v>
       </c>
       <c r="G82">
-        <v>-7.856342515949979</v>
+        <v>0.2126734819584933</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.00931146470419901</v>
       </c>
       <c r="E83">
-        <v>-15.79804555681443</v>
+        <v>-6.799650710392889</v>
       </c>
       <c r="F83">
-        <v>-1.972781139669212</v>
+        <v>0.4323156882321234</v>
       </c>
       <c r="G83">
-        <v>-7.162784152487031</v>
+        <v>-0.845287504231707</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.1472052893350602</v>
       </c>
       <c r="E84">
-        <v>-16.39329535122667</v>
+        <v>-6.777040039672591</v>
       </c>
       <c r="F84">
-        <v>-2.168752986353907</v>
+        <v>0.2793261693438883</v>
       </c>
       <c r="G84">
-        <v>-7.450235567202185</v>
+        <v>-0.3069670139676475</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.257335172237406</v>
       </c>
       <c r="E85">
-        <v>-17.12715720653969</v>
+        <v>-8.761190926133358</v>
       </c>
       <c r="F85">
-        <v>-2.405101116985857</v>
+        <v>0.2676934059063749</v>
       </c>
       <c r="G85">
-        <v>-6.899722057623229</v>
+        <v>0.4970274235215317</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3419285648689756</v>
       </c>
       <c r="E86">
-        <v>-18.33070785745426</v>
+        <v>-8.867990457130256</v>
       </c>
       <c r="F86">
-        <v>-2.307966755333587</v>
+        <v>0.191778503644217</v>
       </c>
       <c r="G86">
-        <v>-6.850027957105439</v>
+        <v>1.1489897412754</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.4078561227382184</v>
       </c>
       <c r="E87">
-        <v>-18.91060159650649</v>
+        <v>-12.29417502117155</v>
       </c>
       <c r="F87">
-        <v>-2.64699848084916</v>
+        <v>-0.1610612781086212</v>
       </c>
       <c r="G87">
-        <v>-6.611017216272367</v>
+        <v>0.2572423144004308</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4647993814295572</v>
       </c>
       <c r="E88">
-        <v>-20.02893542354473</v>
+        <v>-11.98086349000286</v>
       </c>
       <c r="F88">
-        <v>-2.649084309969409</v>
+        <v>-0.1877131709262925</v>
       </c>
       <c r="G88">
-        <v>-7.541499463656581</v>
+        <v>0.6027090075081272</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5226724452638779</v>
       </c>
       <c r="E89">
-        <v>-21.14366458527287</v>
+        <v>-14.74467268941622</v>
       </c>
       <c r="F89">
-        <v>-2.671427035557717</v>
+        <v>-0.2708133320403333</v>
       </c>
       <c r="G89">
-        <v>-6.444478816022751</v>
+        <v>0.05732076600502373</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.5903966179182873</v>
       </c>
       <c r="E90">
-        <v>-22.10452525716838</v>
+        <v>-16.65134591407975</v>
       </c>
       <c r="F90">
-        <v>-2.871374217408448</v>
+        <v>-0.763233849532291</v>
       </c>
       <c r="G90">
-        <v>-6.791330184628532</v>
+        <v>0.1012366353566318</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.6770782827341794</v>
       </c>
       <c r="E91">
-        <v>-23.60339581201918</v>
+        <v>-16.75086365887232</v>
       </c>
       <c r="F91">
-        <v>-2.938776816239438</v>
+        <v>-0.8847073022136162</v>
       </c>
       <c r="G91">
-        <v>-6.820759460795192</v>
+        <v>-0.2189384019708647</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7888908017967535</v>
       </c>
       <c r="E92">
-        <v>-25.59327521809965</v>
+        <v>-19.15056090569894</v>
       </c>
       <c r="F92">
-        <v>-3.096671098519649</v>
+        <v>-0.377844199053849</v>
       </c>
       <c r="G92">
-        <v>-6.969736763258661</v>
+        <v>1.114986442254874</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.9280801811174511</v>
       </c>
       <c r="E93">
-        <v>-28.47499682372473</v>
+        <v>-22.93941736759253</v>
       </c>
       <c r="F93">
-        <v>-3.411534376691144</v>
+        <v>-0.4072835481819407</v>
       </c>
       <c r="G93">
-        <v>-6.981257132153871</v>
+        <v>0.3126949587550465</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.092226770600946</v>
       </c>
       <c r="E94">
-        <v>-29.30826321198012</v>
+        <v>-24.04904746758803</v>
       </c>
       <c r="F94">
-        <v>-3.090566859128419</v>
+        <v>-0.5736197226640815</v>
       </c>
       <c r="G94">
-        <v>-7.050533562938427</v>
+        <v>0.04235839569395583</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.276686505510615</v>
       </c>
       <c r="E95">
-        <v>-30.97823083602572</v>
+        <v>-27.56332896497454</v>
       </c>
       <c r="F95">
-        <v>-3.293955907537782</v>
+        <v>-0.9135941302840405</v>
       </c>
       <c r="G95">
-        <v>-7.732916085769907</v>
+        <v>-0.3727522250129546</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.472501986234218</v>
       </c>
       <c r="E96">
-        <v>-33.1594586470633</v>
+        <v>-28.92434824255784</v>
       </c>
       <c r="F96">
-        <v>-3.517567889351689</v>
+        <v>-1.234982458487387</v>
       </c>
       <c r="G96">
-        <v>-7.583974876743593</v>
+        <v>-0.8766723884477957</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.669439765534723</v>
       </c>
       <c r="E97">
-        <v>-35.65080767933116</v>
+        <v>-31.89879714620098</v>
       </c>
       <c r="F97">
-        <v>-3.801350822570146</v>
+        <v>-1.333626105547558</v>
       </c>
       <c r="G97">
-        <v>-7.753659968468717</v>
+        <v>-0.5446291727397877</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.855715636937669</v>
       </c>
       <c r="E98">
-        <v>-38.30522253214122</v>
+        <v>-34.44515581647702</v>
       </c>
       <c r="F98">
-        <v>-3.802109607111111</v>
+        <v>-1.214127480754507</v>
       </c>
       <c r="G98">
-        <v>-7.976077571875677</v>
+        <v>-0.1047518917021886</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.022577164645044</v>
       </c>
       <c r="E99">
-        <v>-40.52497633579905</v>
+        <v>-37.3005511384585</v>
       </c>
       <c r="F99">
-        <v>-3.639048797339639</v>
+        <v>-1.819039463179235</v>
       </c>
       <c r="G99">
-        <v>-8.239828723266962</v>
+        <v>-1.358135871529797</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.160701316521086</v>
       </c>
       <c r="E100">
-        <v>-43.08468268321271</v>
+        <v>-39.39346238516149</v>
       </c>
       <c r="F100">
-        <v>-3.709062410224254</v>
+        <v>-1.321109474091257</v>
       </c>
       <c r="G100">
-        <v>-8.482386464605794</v>
+        <v>-1.287126955761854</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.265221904530968</v>
       </c>
       <c r="E101">
-        <v>-44.90289669661041</v>
+        <v>-42.73599697733309</v>
       </c>
       <c r="F101">
-        <v>-3.877071886860049</v>
+        <v>-1.801895571410896</v>
       </c>
       <c r="G101">
-        <v>-8.717279272381763</v>
+        <v>-1.773827268452729</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.330111820270115</v>
       </c>
       <c r="E102">
-        <v>-47.83083137948376</v>
+        <v>-44.9518359152113</v>
       </c>
       <c r="F102">
-        <v>-3.789774388116024</v>
+        <v>-1.370495910278761</v>
       </c>
       <c r="G102">
-        <v>-9.062552373417452</v>
+        <v>-2.130627300826748</v>
       </c>
     </row>
   </sheetData>
